--- a/SHOP_Qcut_帳戶餘額.xlsx
+++ b/SHOP_Qcut_帳戶餘額.xlsx
@@ -413,36 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SHAP_Min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SHAP_Max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Feature_Mean</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SHAP_Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SHAP_Median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SHAP_Std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fraud_Prob</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cnt</t>
         </is>
@@ -450,201 +460,261 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>-0.2790000140666962</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.341799974441528</v>
+      </c>
+      <c r="C2" t="n">
         <v>-2003.4536</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>0.5281999707221985</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>0.5296000242233276</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.1777999997138977</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>0.859000027179718</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0.1099999994039536</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.127799987792969</v>
+      </c>
+      <c r="C3" t="n">
         <v>545.2006</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>0.5285999774932861</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>0.5253999829292297</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.128700003027916</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.8622000217437744</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1416</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>0.1814000010490417</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9718000292778015</v>
+      </c>
+      <c r="C4" t="n">
         <v>1670.8356</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>0.5299999713897705</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>0.5270000100135803</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.1237000003457069</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.8610000014305115</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>1405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>0.05249999836087227</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9733999967575073</v>
+      </c>
+      <c r="C5" t="n">
         <v>3695.0526</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>0.4686999917030334</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>0.4693999886512756</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.1367000043392181</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.8633999824523926</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>-0.02070000022649765</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8822000026702881</v>
+      </c>
+      <c r="C6" t="n">
         <v>7806.178</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>0.2743000090122223</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>0.2626999914646149</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.1209999993443489</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.8626000285148621</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>-0.07540000230073929</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7473000288009644</v>
+      </c>
+      <c r="C7" t="n">
         <v>15074.5872</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>0.1986999958753586</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>0.1958000063896179</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.1053000018000603</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>0.8622000217437744</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>-0.2547999918460846</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5345000028610229</v>
+      </c>
+      <c r="C8" t="n">
         <v>24995.601</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>0.1310999989509583</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>0.13230000436306</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.08720000088214874</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.8675000071525574</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1411</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>-0.3222000002861023</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4959999918937683</v>
+      </c>
+      <c r="C9" t="n">
         <v>37889.572</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>0.03139999881386757</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>0.04289999976754189</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.122299998998642</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>0.8676000237464905</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>1409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>-0.5741000175476074</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.213699996471405</v>
+      </c>
+      <c r="C10" t="n">
         <v>61511.7191</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>-0.1706999987363815</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>-0.1730999946594238</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.1322000026702881</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>0.8723999857902527</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>-1.736799955368042</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2978000044822693</v>
+      </c>
+      <c r="C11" t="n">
         <v>189888.3267</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>-0.4745999872684479</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>-0.4244999885559082</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.2720000147819519</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.871399998664856</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>1411</v>
       </c>
     </row>
